--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9502,0.0015,0.0175,0.0126</t>
-  </si>
-  <si>
-    <t>0.0071,0.0005,0.0003,0.9973</t>
-  </si>
-  <si>
-    <t>0.9473,0.0020,0.0006,0.0688</t>
-  </si>
-  <si>
-    <t>0.0542,0.0017,0.0002,0.9856</t>
-  </si>
-  <si>
-    <t>0.9934,0.0043,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0004,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9930,0.0016,0.0004,0.0017</t>
-  </si>
-  <si>
-    <t>0.9844,0.0074,0.0009,0.0023</t>
-  </si>
-  <si>
-    <t>0.9934,0.0020,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.8421,0.0101,0.2189,0.0022</t>
-  </si>
-  <si>
-    <t>0.0164,0.0113,0.9741,0.0060</t>
-  </si>
-  <si>
-    <t>0.4032,0.0070,0.7938,0.0005</t>
-  </si>
-  <si>
-    <t>0.0091,0.0016,0.9889,0.0012</t>
-  </si>
-  <si>
-    <t>0.9129,0.0090,0.1257,0.0024</t>
-  </si>
-  <si>
-    <t>0.0008,0.9963,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.0027,0.9937,0.0049,0.0006</t>
-  </si>
-  <si>
-    <t>0.0946,0.9194,0.0044,0.0025</t>
-  </si>
-  <si>
-    <t>0.0015,0.9969,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.6154,0.0044,0.5714,0.0012</t>
-  </si>
-  <si>
-    <t>0.1439,0.0071,0.8896,0.0028</t>
-  </si>
-  <si>
-    <t>0.0215,0.0022,0.9797,0.0007</t>
-  </si>
-  <si>
-    <t>0.0091,0.0046,0.9760,0.0097</t>
-  </si>
-  <si>
-    <t>0.0790,0.0102,0.9355,0.0032</t>
-  </si>
-  <si>
-    <t>0.0248,0.0010,0.9784,0.0014</t>
-  </si>
-  <si>
-    <t>0.0065,0.0008,0.9906,0.0010</t>
-  </si>
-  <si>
-    <t>0.9082,0.1070,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.5863,0.5681,0.0246,0.0021</t>
-  </si>
-  <si>
-    <t>0.0140,0.0828,0.9603,0.0114</t>
-  </si>
-  <si>
-    <t>0.0115,0.9673,0.0247,0.0011</t>
-  </si>
-  <si>
-    <t>0.9546,0.0137,0.0036,0.0164</t>
-  </si>
-  <si>
-    <t>0.1554,0.1597,0.7638,0.0158</t>
-  </si>
-  <si>
-    <t>0.6442,0.3794,0.1217,0.0139</t>
-  </si>
-  <si>
-    <t>0.0153,0.9769,0.0541,0.0016</t>
-  </si>
-  <si>
-    <t>0.0332,0.3327,0.5132,0.1304</t>
-  </si>
-  <si>
-    <t>0.6910,0.0168,0.3597,0.0103</t>
-  </si>
-  <si>
-    <t>0.0193,0.0120,0.9649,0.0130</t>
-  </si>
-  <si>
-    <t>0.1373,0.0070,0.7862,0.0397</t>
-  </si>
-  <si>
-    <t>0.0580,0.0874,0.9410,0.0023</t>
-  </si>
-  <si>
-    <t>0.0152,0.9536,0.0195,0.0018</t>
-  </si>
-  <si>
-    <t>0.0083,0.0048,0.9732,0.0127</t>
-  </si>
-  <si>
-    <t>0.0088,0.8777,0.0041,0.4336</t>
-  </si>
-  <si>
-    <t>0.0022,0.9891,0.0054,0.0051</t>
-  </si>
-  <si>
-    <t>0.0027,0.9899,0.0406,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.9947,0.0092,0.0052</t>
-  </si>
-  <si>
-    <t>0.0025,0.0420,0.9866,0.0039</t>
-  </si>
-  <si>
-    <t>0.0113,0.0886,0.9656,0.0024</t>
-  </si>
-  <si>
-    <t>0.0100,0.0065,0.9887,0.0006</t>
-  </si>
-  <si>
-    <t>0.0026,0.0008,0.9954,0.0006</t>
-  </si>
-  <si>
-    <t>0.0051,0.0078,0.9883,0.0012</t>
-  </si>
-  <si>
-    <t>0.0097,0.0020,0.9913,0.0001</t>
-  </si>
-  <si>
-    <t>0.9269,0.0907,0.0128,0.0019</t>
-  </si>
-  <si>
-    <t>0.9858,0.0040,0.0060,0.0013</t>
-  </si>
-  <si>
-    <t>0.9858,0.0050,0.0023,0.0030</t>
-  </si>
-  <si>
-    <t>0.0026,0.0101,0.9897,0.0240</t>
-  </si>
-  <si>
-    <t>0.9897,0.0040,0.0014,0.0016</t>
-  </si>
-  <si>
-    <t>0.9944,0.0030,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9926,0.0047,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.8537,0.9645,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0020,0.9966,0.0025</t>
-  </si>
-  <si>
-    <t>0.0019,0.0314,0.9863,0.0064</t>
-  </si>
-  <si>
-    <t>0.0002,0.8940,0.9929,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9977,0.0034</t>
-  </si>
-  <si>
-    <t>0.0030,0.9952,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.9935,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0010,0.0077,0.0007</t>
-  </si>
-  <si>
-    <t>0.8960,0.0963,0.0262,0.0025</t>
-  </si>
-  <si>
-    <t>0.0074,0.0156,0.9904,0.0008</t>
-  </si>
-  <si>
-    <t>0.0016,0.9796,0.4330,0.0004</t>
-  </si>
-  <si>
-    <t>0.0013,0.9874,0.1373,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9957,0.3021,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9605,0.9844,0.0002</t>
-  </si>
-  <si>
-    <t>0.0073,0.0013,0.0151,0.9910</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.0009,0.9991</t>
-  </si>
-  <si>
-    <t>0.0045,0.0001,0.0008,0.9978</t>
-  </si>
-  <si>
-    <t>0.0241,0.0015,0.0005,0.9903</t>
-  </si>
-  <si>
-    <t>0.0087,0.0009,0.0206,0.9888</t>
-  </si>
-  <si>
-    <t>0.0019,0.0002,0.0010,0.9986</t>
-  </si>
-  <si>
-    <t>0.0029,0.9633,0.7773,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.9644,0.9577,0.0002</t>
-  </si>
-  <si>
-    <t>0.0192,0.5031,0.8214,0.0024</t>
-  </si>
-  <si>
-    <t>0.0038,0.4965,0.9648,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9970,0.1040,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.9624,0.3875,0.0005</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9966,0.0011,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9896,0.0064,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9963,0.0010,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9953,0.0008,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9972,0.0006,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9961,0.0023,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9929,0.0040,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9971,0.0004,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0009,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0002</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9928,0.0009,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.0167,0.0030,0.0001,0.9934</t>
+  </si>
+  <si>
+    <t>0.9604,0.0026,0.0031,0.0252</t>
+  </si>
+  <si>
+    <t>0.0599,0.0097,0.0036,0.9658</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0013,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9870,0.0101,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9970,0.0006,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.7739,0.1282,0.1591,0.0061</t>
+  </si>
+  <si>
+    <t>0.0107,0.0064,0.9805,0.0031</t>
+  </si>
+  <si>
+    <t>0.4534,0.0234,0.6485,0.0004</t>
+  </si>
+  <si>
+    <t>0.0029,0.0022,0.9895,0.0092</t>
+  </si>
+  <si>
+    <t>0.9645,0.0133,0.0171,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9986,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.9962,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.0776,0.9406,0.0052,0.0012</t>
+  </si>
+  <si>
+    <t>0.0022,0.9960,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.6031,0.0127,0.4884,0.0122</t>
+  </si>
+  <si>
+    <t>0.2034,0.0061,0.8581,0.0024</t>
+  </si>
+  <si>
+    <t>0.0047,0.0009,0.9928,0.0007</t>
+  </si>
+  <si>
+    <t>0.0076,0.0013,0.9893,0.0009</t>
+  </si>
+  <si>
+    <t>0.4281,0.0025,0.7989,0.0006</t>
+  </si>
+  <si>
+    <t>0.0113,0.0053,0.9850,0.0012</t>
+  </si>
+  <si>
+    <t>0.0023,0.0007,0.9934,0.0016</t>
+  </si>
+  <si>
+    <t>0.9603,0.0364,0.0094,0.0007</t>
+  </si>
+  <si>
+    <t>0.8002,0.1203,0.0966,0.0091</t>
+  </si>
+  <si>
+    <t>0.0045,0.0649,0.9807,0.0123</t>
+  </si>
+  <si>
+    <t>0.0112,0.9694,0.0153,0.0004</t>
+  </si>
+  <si>
+    <t>0.8048,0.0870,0.0812,0.0747</t>
+  </si>
+  <si>
+    <t>0.4939,0.1733,0.3241,0.0190</t>
+  </si>
+  <si>
+    <t>0.7872,0.3454,0.0115,0.0016</t>
+  </si>
+  <si>
+    <t>0.0158,0.9724,0.1146,0.0009</t>
+  </si>
+  <si>
+    <t>0.0650,0.7072,0.1774,0.0139</t>
+  </si>
+  <si>
+    <t>0.4419,0.0141,0.6936,0.0032</t>
+  </si>
+  <si>
+    <t>0.0498,0.0126,0.9186,0.0202</t>
+  </si>
+  <si>
+    <t>0.0483,0.0144,0.9400,0.0076</t>
+  </si>
+  <si>
+    <t>0.2095,0.0196,0.8675,0.0012</t>
+  </si>
+  <si>
+    <t>0.0072,0.9690,0.0343,0.0009</t>
+  </si>
+  <si>
+    <t>0.0064,0.0106,0.9866,0.0021</t>
+  </si>
+  <si>
+    <t>0.0282,0.4046,0.0104,0.8517</t>
+  </si>
+  <si>
+    <t>0.0029,0.9884,0.0029,0.0048</t>
+  </si>
+  <si>
+    <t>0.0097,0.9815,0.0099,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.9932,0.0053,0.0063</t>
+  </si>
+  <si>
+    <t>0.0007,0.1600,0.9951,0.0007</t>
+  </si>
+  <si>
+    <t>0.0061,0.0734,0.9665,0.0091</t>
+  </si>
+  <si>
+    <t>0.0071,0.0061,0.9911,0.0006</t>
+  </si>
+  <si>
+    <t>0.0067,0.0008,0.9903,0.0012</t>
+  </si>
+  <si>
+    <t>0.0030,0.0054,0.9946,0.0003</t>
+  </si>
+  <si>
+    <t>0.0166,0.0257,0.9652,0.0009</t>
+  </si>
+  <si>
+    <t>0.9761,0.0288,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9833,0.0106,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9882,0.0060,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.0132,0.0047,0.9852,0.0028</t>
+  </si>
+  <si>
+    <t>0.9881,0.0096,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9875,0.0099,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9876,0.0095,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0055,0.6179,0.9605,0.0026</t>
+  </si>
+  <si>
+    <t>0.0071,0.0088,0.9918,0.0010</t>
+  </si>
+  <si>
+    <t>0.0062,0.1437,0.8876,0.0493</t>
+  </si>
+  <si>
+    <t>0.0002,0.9837,0.9816,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9988,0.0069</t>
+  </si>
+  <si>
+    <t>0.0100,0.9846,0.0034,0.0004</t>
+  </si>
+  <si>
+    <t>0.0041,0.9935,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9647,0.0027,0.0495,0.0010</t>
+  </si>
+  <si>
+    <t>0.7552,0.0653,0.1412,0.1142</t>
+  </si>
+  <si>
+    <t>0.0070,0.0258,0.9920,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.9880,0.3862,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.9874,0.2663,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9973,0.0262,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9774,0.9730,0.0002</t>
+  </si>
+  <si>
+    <t>0.0106,0.0005,0.0100,0.9907</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0137,0.0039,0.0003,0.9940</t>
+  </si>
+  <si>
+    <t>0.0274,0.0003,0.0006,0.9927</t>
+  </si>
+  <si>
+    <t>0.0263,0.0005,0.0011,0.9913</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.0005,0.9993</t>
+  </si>
+  <si>
+    <t>0.0065,0.9525,0.4206,0.0010</t>
+  </si>
+  <si>
+    <t>0.0028,0.9309,0.8327,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.9719,0.2657,0.0004</t>
+  </si>
+  <si>
+    <t>0.0023,0.7705,0.9745,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.9874,0.7416,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9759,0.1881,0.0013</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9929,0.0052,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9807,0.0121,0.0009,0.0029</t>
+  </si>
+  <si>
+    <t>0.9920,0.0036,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9845,0.0076,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0009,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9992,0.0001,0.0000,0.0002</t>
   </si>
   <si>
-    <t>0.9910,0.0087,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9968,0.0005,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0129,0.0006,0.9855,0.0013</t>
-  </si>
-  <si>
-    <t>0.0484,0.0158,0.9542,0.0024</t>
-  </si>
-  <si>
-    <t>0.9791,0.0011,0.0028,0.0054</t>
-  </si>
-  <si>
-    <t>0.0914,0.0025,0.9427,0.0011</t>
-  </si>
-  <si>
-    <t>0.0052,0.9887,0.0081,0.0023</t>
-  </si>
-  <si>
-    <t>0.0022,0.9924,0.0189,0.0022</t>
-  </si>
-  <si>
-    <t>0.0053,0.9927,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.0322,0.9626,0.0115,0.0034</t>
-  </si>
-  <si>
-    <t>0.0027,0.9941,0.0153,0.0004</t>
-  </si>
-  <si>
-    <t>0.0043,0.9884,0.0246,0.0040</t>
-  </si>
-  <si>
-    <t>0.0765,0.9463,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.1111,0.7407,0.3288,0.0689</t>
-  </si>
-  <si>
-    <t>0.3268,0.0056,0.8177,0.0008</t>
-  </si>
-  <si>
-    <t>0.6055,0.2911,0.0998,0.0234</t>
-  </si>
-  <si>
-    <t>0.8002,0.0250,0.2471,0.0096</t>
-  </si>
-  <si>
-    <t>0.2287,0.1236,0.3253,0.6084</t>
-  </si>
-  <si>
-    <t>0.0004,0.9970,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.9898,0.0021,0.0139</t>
-  </si>
-  <si>
-    <t>0.0006,0.9951,0.6057,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9911,0.1563,0.0004</t>
-  </si>
-  <si>
-    <t>0.0159,0.9823,0.0139,0.0005</t>
-  </si>
-  <si>
-    <t>0.8328,0.3026,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.9937,0.0012,0.0010,0.0019</t>
-  </si>
-  <si>
-    <t>0.9909,0.0015,0.0010,0.0036</t>
-  </si>
-  <si>
-    <t>0.9970,0.0006,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9770,0.0057,0.0113,0.0049</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9969,0.0005,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9835,0.0039,0.0010,0.0058</t>
-  </si>
-  <si>
-    <t>0.9863,0.0047,0.0065,0.0006</t>
-  </si>
-  <si>
-    <t>0.0015,0.9546,0.7740,0.0011</t>
-  </si>
-  <si>
-    <t>0.0037,0.9118,0.9177,0.0010</t>
-  </si>
-  <si>
-    <t>0.0412,0.0126,0.9741,0.0001</t>
-  </si>
-  <si>
-    <t>0.0802,0.0270,0.9198,0.0017</t>
-  </si>
-  <si>
-    <t>0.9904,0.0008,0.0058,0.0003</t>
-  </si>
-  <si>
-    <t>0.8784,0.0013,0.2923,0.0003</t>
-  </si>
-  <si>
-    <t>0.0675,0.0006,0.9407,0.0038</t>
-  </si>
-  <si>
-    <t>0.8842,0.0504,0.0898,0.0041</t>
-  </si>
-  <si>
-    <t>0.1710,0.0004,0.0051,0.9239</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0031,0.9995</t>
-  </si>
-  <si>
-    <t>0.0012,0.0013,0.0029,0.9979</t>
-  </si>
-  <si>
-    <t>0.0213,0.0005,0.0002,0.9940</t>
-  </si>
-  <si>
-    <t>0.0025,0.7219,0.9409,0.0013</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0060,0.9830,0.0007,0.0270</t>
-  </si>
-  <si>
-    <t>0.9958,0.0005,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.1163,0.8938,0.0122,0.0042</t>
-  </si>
-  <si>
-    <t>0.9880,0.0024,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.5426,0.0266,0.0161,0.6418</t>
-  </si>
-  <si>
-    <t>0.9967,0.0003,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0850,0.9958,0.0026</t>
-  </si>
-  <si>
-    <t>0.9131,0.0003,0.0008,0.1793</t>
-  </si>
-  <si>
-    <t>0.9652,0.0006,0.0009,0.0475</t>
-  </si>
-  <si>
-    <t>0.5824,0.3308,0.1435,0.0105</t>
-  </si>
-  <si>
-    <t>0.9820,0.0052,0.0049,0.0021</t>
-  </si>
-  <si>
-    <t>0.9494,0.0241,0.0239,0.0058</t>
-  </si>
-  <si>
-    <t>0.2255,0.8051,0.0447,0.0048</t>
-  </si>
-  <si>
-    <t>0.9012,0.0439,0.0698,0.0011</t>
-  </si>
-  <si>
-    <t>0.9797,0.0150,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.9947,0.0007,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9951,0.0023,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9908,0.0027,0.0038,0.0009</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9927,0.0038,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9915,0.0028,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9927,0.0017,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9137,0.1113,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.9524,0.0559,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.1063,0.9342,0.0050,0.0009</t>
-  </si>
-  <si>
-    <t>0.0234,0.0177,0.9670,0.0075</t>
-  </si>
-  <si>
-    <t>0.9961,0.0019,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9881,0.0079,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.9817,0.0100,0.0066,0.0009</t>
-  </si>
-  <si>
-    <t>0.9668,0.0289,0.0035,0.0018</t>
-  </si>
-  <si>
-    <t>0.0007,0.0160,0.9979,0.0005</t>
-  </si>
-  <si>
-    <t>0.9456,0.0467,0.0038,0.0053</t>
-  </si>
-  <si>
-    <t>0.0018,0.0059,0.9951,0.0011</t>
-  </si>
-  <si>
-    <t>0.0277,0.0238,0.9724,0.0012</t>
-  </si>
-  <si>
-    <t>0.0025,0.0018,0.9952,0.0008</t>
-  </si>
-  <si>
-    <t>0.0259,0.0158,0.9597,0.0024</t>
-  </si>
-  <si>
-    <t>0.0017,0.0027,0.9970,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.0011,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.0041,0.0032,0.9939,0.0006</t>
-  </si>
-  <si>
-    <t>0.0223,0.0138,0.9745,0.0020</t>
-  </si>
-  <si>
-    <t>0.6709,0.0098,0.4226,0.0061</t>
-  </si>
-  <si>
-    <t>0.4165,0.0062,0.5312,0.0273</t>
-  </si>
-  <si>
-    <t>0.0696,0.0138,0.9288,0.0030</t>
-  </si>
-  <si>
-    <t>0.0831,0.0424,0.8941,0.0039</t>
-  </si>
-  <si>
-    <t>0.6939,0.0257,0.4127,0.0018</t>
-  </si>
-  <si>
-    <t>0.6687,0.0659,0.4046,0.0105</t>
-  </si>
-  <si>
-    <t>0.4575,0.0184,0.6881,0.0092</t>
-  </si>
-  <si>
-    <t>0.0643,0.9577,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.3094,0.8286,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.1082,0.9218,0.0042,0.0019</t>
-  </si>
-  <si>
-    <t>0.9901,0.0083,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.5133,0.6486,0.0015,0.0014</t>
-  </si>
-  <si>
-    <t>0.6963,0.0456,0.2277,0.0567</t>
-  </si>
-  <si>
-    <t>0.9655,0.0029,0.0307,0.0010</t>
-  </si>
-  <si>
-    <t>0.9721,0.0034,0.0101,0.0032</t>
-  </si>
-  <si>
-    <t>0.8235,0.0037,0.1896,0.0100</t>
-  </si>
-  <si>
-    <t>0.9370,0.0005,0.0813,0.0008</t>
-  </si>
-  <si>
-    <t>0.0044,0.0158,0.9835,0.0160</t>
-  </si>
-  <si>
-    <t>0.0146,0.1046,0.9277,0.0115</t>
-  </si>
-  <si>
-    <t>0.3340,0.0202,0.7735,0.0013</t>
-  </si>
-  <si>
-    <t>0.0299,0.0151,0.9633,0.0030</t>
-  </si>
-  <si>
-    <t>0.0115,0.3290,0.9131,0.0011</t>
-  </si>
-  <si>
-    <t>0.9941,0.0022,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9882,0.0040,0.0061,0.0009</t>
-  </si>
-  <si>
-    <t>0.9793,0.0156,0.0015,0.0014</t>
-  </si>
-  <si>
-    <t>0.9917,0.0054,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9907,0.0042,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9928,0.0031,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9976,0.0003,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0036,0.0039,0.9908,0.0053</t>
-  </si>
-  <si>
-    <t>0.1457,0.7370,0.1290,0.0847</t>
-  </si>
-  <si>
-    <t>0.9474,0.0047,0.0303,0.0130</t>
-  </si>
-  <si>
-    <t>0.0282,0.0091,0.9743,0.0012</t>
-  </si>
-  <si>
-    <t>0.0038,0.0115,0.9893,0.0022</t>
-  </si>
-  <si>
-    <t>0.0152,0.0225,0.9715,0.0021</t>
-  </si>
-  <si>
-    <t>0.0045,0.0031,0.9915,0.0025</t>
-  </si>
-  <si>
-    <t>0.0460,0.0139,0.9362,0.0101</t>
-  </si>
-  <si>
-    <t>0.0033,0.0025,0.9951,0.0006</t>
-  </si>
-  <si>
-    <t>0.0076,0.0163,0.9721,0.0163</t>
-  </si>
-  <si>
-    <t>0.0153,0.0181,0.9721,0.0073</t>
-  </si>
-  <si>
-    <t>0.8301,0.0014,0.3015,0.0005</t>
-  </si>
-  <si>
-    <t>0.7737,0.0045,0.3679,0.0012</t>
-  </si>
-  <si>
-    <t>0.9730,0.0015,0.0278,0.0013</t>
-  </si>
-  <si>
-    <t>0.9938,0.0033,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9936,0.0026,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9958,0.0019,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9719,0.0277,0.0029,0.0016</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.9872,0.0147,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.0094,0.0291,0.9702,0.0017</t>
-  </si>
-  <si>
-    <t>0.0096,0.0176,0.9852,0.0003</t>
-  </si>
-  <si>
-    <t>0.0188,0.0608,0.9657,0.0119</t>
-  </si>
-  <si>
-    <t>0.0072,0.8064,0.4385,0.0067</t>
-  </si>
-  <si>
-    <t>0.0019,0.0026,0.9927,0.0049</t>
-  </si>
-  <si>
-    <t>0.0260,0.0023,0.9503,0.0189</t>
-  </si>
-  <si>
-    <t>0.0091,0.0133,0.9822,0.0056</t>
-  </si>
-  <si>
-    <t>0.2946,0.0194,0.7710,0.0048</t>
-  </si>
-  <si>
-    <t>0.7803,0.0008,0.0030,0.3346</t>
-  </si>
-  <si>
-    <t>0.0707,0.0063,0.0029,0.9685</t>
-  </si>
-  <si>
-    <t>0.0184,0.0001,0.0014,0.9926</t>
-  </si>
-  <si>
-    <t>0.0029,0.0000,0.0003,0.9987</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.0061,0.9986</t>
-  </si>
-  <si>
-    <t>0.8843,0.0233,0.0037,0.0648</t>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.0063,0.0002,0.9888,0.0031</t>
+  </si>
+  <si>
+    <t>0.0111,0.0037,0.9848,0.0009</t>
+  </si>
+  <si>
+    <t>0.9487,0.0022,0.0136,0.0145</t>
+  </si>
+  <si>
+    <t>0.0070,0.0005,0.9914,0.0006</t>
+  </si>
+  <si>
+    <t>0.0068,0.9854,0.0064,0.0050</t>
+  </si>
+  <si>
+    <t>0.0033,0.9923,0.0071,0.0010</t>
+  </si>
+  <si>
+    <t>0.2165,0.8626,0.0045,0.0008</t>
+  </si>
+  <si>
+    <t>0.0033,0.9923,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.0016,0.9960,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9979,0.0034,0.0007</t>
+  </si>
+  <si>
+    <t>0.0329,0.9549,0.0022,0.0072</t>
+  </si>
+  <si>
+    <t>0.7151,0.0530,0.3471,0.0065</t>
+  </si>
+  <si>
+    <t>0.0334,0.0038,0.9628,0.0035</t>
+  </si>
+  <si>
+    <t>0.6269,0.0654,0.3188,0.0330</t>
+  </si>
+  <si>
+    <t>0.8215,0.0381,0.1859,0.0024</t>
+  </si>
+  <si>
+    <t>0.0189,0.0339,0.1611,0.9481</t>
+  </si>
+  <si>
+    <t>0.0022,0.9948,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9979,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.9909,0.0087,0.0280</t>
+  </si>
+  <si>
+    <t>0.0004,0.9890,0.9009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.9924,0.0466,0.0002</t>
+  </si>
+  <si>
+    <t>0.1656,0.9018,0.0066,0.0013</t>
+  </si>
+  <si>
+    <t>0.6610,0.4852,0.0054,0.0016</t>
+  </si>
+  <si>
+    <t>0.9934,0.0017,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9912,0.0026,0.0011,0.0019</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9825,0.0045,0.0034,0.0063</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9766,0.0105,0.0035,0.0039</t>
+  </si>
+  <si>
+    <t>0.9953,0.0011,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.0070,0.6004,0.8703,0.0041</t>
+  </si>
+  <si>
+    <t>0.0030,0.8226,0.9566,0.0006</t>
+  </si>
+  <si>
+    <t>0.0063,0.0262,0.9891,0.0006</t>
+  </si>
+  <si>
+    <t>0.0186,0.0563,0.9490,0.0045</t>
+  </si>
+  <si>
+    <t>0.9962,0.0004,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9000,0.0051,0.1429,0.0015</t>
+  </si>
+  <si>
+    <t>0.1916,0.0009,0.9178,0.0003</t>
+  </si>
+  <si>
+    <t>0.8854,0.0246,0.1267,0.0038</t>
+  </si>
+  <si>
+    <t>0.2395,0.0003,0.0004,0.9403</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0200,0.9991</t>
+  </si>
+  <si>
+    <t>0.0024,0.0074,0.0015,0.9971</t>
+  </si>
+  <si>
+    <t>0.0073,0.0006,0.0057,0.9934</t>
+  </si>
+  <si>
+    <t>0.0043,0.3256,0.9577,0.0040</t>
+  </si>
+  <si>
+    <t>0.9957,0.0014,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.0308,0.9450,0.0017,0.0307</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0427,0.9535,0.0140,0.0060</t>
+  </si>
+  <si>
+    <t>0.9877,0.0026,0.0029,0.0022</t>
+  </si>
+  <si>
+    <t>0.6212,0.0049,0.0077,0.5082</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0674,0.9933,0.0057</t>
+  </si>
+  <si>
+    <t>0.6544,0.0002,0.0012,0.5954</t>
+  </si>
+  <si>
+    <t>0.9718,0.0023,0.0046,0.0152</t>
+  </si>
+  <si>
+    <t>0.0441,0.9520,0.0175,0.0023</t>
+  </si>
+  <si>
+    <t>0.9914,0.0037,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9748,0.0260,0.0034,0.0007</t>
+  </si>
+  <si>
+    <t>0.2500,0.7773,0.0363,0.0170</t>
+  </si>
+  <si>
+    <t>0.9407,0.0636,0.0093,0.0009</t>
+  </si>
+  <si>
+    <t>0.9650,0.0267,0.0092,0.0016</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0011,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9942,0.0028,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9920,0.0007,0.0014,0.0048</t>
+  </si>
+  <si>
+    <t>0.9935,0.0011,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.9792,0.0118,0.0052,0.0006</t>
+  </si>
+  <si>
+    <t>0.9955,0.0007,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9355,0.1107,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.6389,0.4610,0.0087,0.0020</t>
+  </si>
+  <si>
+    <t>0.1597,0.8734,0.0060,0.0017</t>
+  </si>
+  <si>
+    <t>0.7844,0.0292,0.2149,0.0044</t>
+  </si>
+  <si>
+    <t>0.9930,0.0055,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9851,0.0080,0.0061,0.0007</t>
+  </si>
+  <si>
+    <t>0.9951,0.0019,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9799,0.0098,0.0042,0.0017</t>
+  </si>
+  <si>
+    <t>0.0027,0.0121,0.9954,0.0011</t>
+  </si>
+  <si>
+    <t>0.9800,0.0123,0.0019,0.0037</t>
+  </si>
+  <si>
+    <t>0.0046,0.0027,0.9925,0.0005</t>
+  </si>
+  <si>
+    <t>0.0127,0.0126,0.9795,0.0014</t>
+  </si>
+  <si>
+    <t>0.0018,0.0015,0.9969,0.0004</t>
+  </si>
+  <si>
+    <t>0.0222,0.0177,0.9595,0.0050</t>
+  </si>
+  <si>
+    <t>0.0021,0.0126,0.9943,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.0088,0.9800,0.0073</t>
+  </si>
+  <si>
+    <t>0.0277,0.0095,0.9796,0.0011</t>
+  </si>
+  <si>
+    <t>0.0978,0.0062,0.9385,0.0013</t>
+  </si>
+  <si>
+    <t>0.1334,0.1002,0.8279,0.0123</t>
+  </si>
+  <si>
+    <t>0.8019,0.0087,0.3154,0.0005</t>
+  </si>
+  <si>
+    <t>0.0850,0.0152,0.9360,0.0005</t>
+  </si>
+  <si>
+    <t>0.7148,0.0124,0.4231,0.0031</t>
+  </si>
+  <si>
+    <t>0.7099,0.0085,0.4185,0.0075</t>
+  </si>
+  <si>
+    <t>0.4921,0.0439,0.5557,0.0333</t>
+  </si>
+  <si>
+    <t>0.0802,0.9310,0.0137,0.0014</t>
+  </si>
+  <si>
+    <t>0.0305,0.9655,0.0111,0.0013</t>
+  </si>
+  <si>
+    <t>0.3372,0.7452,0.0079,0.0025</t>
+  </si>
+  <si>
+    <t>0.9752,0.0349,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9135,0.1411,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.8274,0.1577,0.0242,0.0038</t>
+  </si>
+  <si>
+    <t>0.9557,0.0015,0.0691,0.0004</t>
+  </si>
+  <si>
+    <t>0.9409,0.0061,0.0374,0.0056</t>
+  </si>
+  <si>
+    <t>0.2786,0.0133,0.7354,0.0252</t>
+  </si>
+  <si>
+    <t>0.9670,0.0008,0.0492,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.0071,0.9859,0.0143</t>
+  </si>
+  <si>
+    <t>0.0565,0.0797,0.9012,0.0065</t>
+  </si>
+  <si>
+    <t>0.0373,0.4657,0.7697,0.0039</t>
+  </si>
+  <si>
+    <t>0.0185,0.0070,0.9800,0.0011</t>
+  </si>
+  <si>
+    <t>0.0077,0.8857,0.3088,0.0014</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9970,0.0008,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9918,0.0035,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9897,0.0060,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9822,0.0132,0.0021,0.0020</t>
+  </si>
+  <si>
+    <t>0.9931,0.0058,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9945,0.0006,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.0020,0.0063,0.9921,0.0056</t>
+  </si>
+  <si>
+    <t>0.3877,0.2007,0.4262,0.0065</t>
+  </si>
+  <si>
+    <t>0.8275,0.0021,0.1335,0.0110</t>
+  </si>
+  <si>
+    <t>0.0129,0.0058,0.9880,0.0006</t>
+  </si>
+  <si>
+    <t>0.0086,0.0015,0.9920,0.0002</t>
+  </si>
+  <si>
+    <t>0.0234,0.0206,0.9620,0.0024</t>
+  </si>
+  <si>
+    <t>0.0027,0.0018,0.9910,0.0048</t>
+  </si>
+  <si>
+    <t>0.0045,0.0147,0.9848,0.0055</t>
+  </si>
+  <si>
+    <t>0.0119,0.0067,0.9827,0.0029</t>
+  </si>
+  <si>
+    <t>0.0186,0.0074,0.9636,0.0158</t>
+  </si>
+  <si>
+    <t>0.1070,0.0937,0.8124,0.0405</t>
+  </si>
+  <si>
+    <t>0.6068,0.0137,0.3998,0.0183</t>
+  </si>
+  <si>
+    <t>0.8895,0.0024,0.1086,0.0052</t>
+  </si>
+  <si>
+    <t>0.9868,0.0008,0.0129,0.0003</t>
+  </si>
+  <si>
+    <t>0.9925,0.0025,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9907,0.0056,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9958,0.0010,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9907,0.0054,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0012,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0132,0.0042,0.9831,0.0009</t>
+  </si>
+  <si>
+    <t>0.0112,0.0191,0.9841,0.0006</t>
+  </si>
+  <si>
+    <t>0.0724,0.0220,0.9328,0.0027</t>
+  </si>
+  <si>
+    <t>0.0555,0.0339,0.9254,0.0033</t>
+  </si>
+  <si>
+    <t>0.0071,0.0038,0.9926,0.0002</t>
+  </si>
+  <si>
+    <t>0.0231,0.0051,0.9622,0.0106</t>
+  </si>
+  <si>
+    <t>0.0360,0.0028,0.9596,0.0063</t>
+  </si>
+  <si>
+    <t>0.2864,0.0026,0.7690,0.0049</t>
+  </si>
+  <si>
+    <t>0.9454,0.0022,0.0109,0.0293</t>
+  </si>
+  <si>
+    <t>0.0887,0.0063,0.0084,0.9613</t>
+  </si>
+  <si>
+    <t>0.0283,0.0009,0.0017,0.9895</t>
+  </si>
+  <si>
+    <t>0.0045,0.0001,0.0009,0.9981</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0003,0.9997</t>
+  </si>
+  <si>
+    <t>0.6541,0.0363,0.0269,0.2512</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2258,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2368,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2426,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2468,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2482,10 +2491,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2566,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2956,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2970,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3084,10 +3093,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3126,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3140,10 +3149,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3166,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3546,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,7 +3600,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3994,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4062,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4078,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4120,10 +4129,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4148,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>366</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4596,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4624,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4734,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4750,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4890,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5030,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5366,10 +5375,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
